--- a/data/2026-08/flujo_licitaciones_2026-08-31.xlsx
+++ b/data/2026-08/flujo_licitaciones_2026-08-31.xlsx
@@ -7,7 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="⏳ Licitaciones Abiertas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="✅ Adjudicados con CUIT" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="🔗 Flujo Cruzado" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="⏳ Licitaciones Abiertas" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,6 +415,341 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:K2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>fecha_extraccion</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>fecha_publicacion</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>organismo_contratante</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>tipo_proceso</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>aviso_id</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>link</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>proveedor_adjudicado</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>cuit_proveedor</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>monto_adjudicado</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>texto_muestra</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>fuente</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>AGENCIA DE RECAUDACIÓN Y CONTROL ADUANERO - DIRECCIÓN REGIONAL ADUANERA CUYO</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Licitación Pública 27/23</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2416807</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2416807/20260831</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>COPA S.R.L</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>30711879850</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>$28.483.116,00</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/pdf/linkQR/VmpiT2gxN25mOUZSbkVWUVVZR3c4dz09
+AGENCIA DE RECAUDACIÓN Y CONTROL ADUANERO -
+DIRECCIÓN REGIONAL ADUANERA CUYO
+Licitación Pública 27/23
+Expediente Nº: EX-2023-01325092- -AFIP-SECFDVAFCE#SDGOAI Objeto de la contratación: Alquiler
+depósito de secuestros y</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>BORA Adjudicaciones</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:U2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>fecha</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>organismo_contratante</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>tipo_proceso_bora</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>link_bora</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>proveedor_adjudicado</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>cuit_proveedor</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>monto_adjudicado_bora</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>en_comprar</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>procesos_comprar</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>unidad_comprar</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>nro_proceso_comprar</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>cobro_en_tgn</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>beneficiario_tgn</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>monto_cobrado_tgn</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>metodo_cruce_tgn</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>etapa</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>alerta</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>indicadores_riesgo</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>score_riesgo_licit</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>indice_riesgo_licit</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>nivel_riesgo_licit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>AGENCIA DE RECAUDACIÓN Y CONTROL ADUANERO - DIRECCIÓN REGIONAL ADUANERA CUYO</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Licitación Pública 27/23</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2416807/20260831</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>COPA S.R.L</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>30711879850</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>$28.483.116,00</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>❌ NO</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>❌ NO</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>✅ ADJUDICADO (sin pago aún)</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>📋 SOLO BORA</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>✅ Sin alertas</t>
+        </is>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
